--- a/src/nodes/HPC/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/HPC/compressor_blade_self_frequency.xlsx
@@ -543,58 +543,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>301.8074886276238</v>
+        <v>320.81601986011196</v>
       </c>
       <c r="C3">
-        <v>1891.5317607808574</v>
+        <v>2010.6647906322426</v>
       </c>
       <c r="D3">
-        <v>5296.8764873956216</v>
+        <v>5630.4859766867248</v>
       </c>
       <c r="E3">
-        <v>10387.543075254751</v>
+        <v>11041.774479096477</v>
       </c>
       <c r="F3">
-        <v>17164.307499580205</v>
+        <v>18245.355145791389</v>
       </c>
       <c r="G3">
-        <v>25633.915224811142</v>
+        <v>27248.398286107782</v>
       </c>
       <c r="H3">
-        <v>1283.122736674598</v>
+        <v>1538.8528722299468</v>
       </c>
       <c r="I3">
-        <v>3849.3682100237938</v>
+        <v>4616.55861668984</v>
       </c>
       <c r="J3">
-        <v>6415.6136833729888</v>
+        <v>7694.2643611497333</v>
       </c>
       <c r="K3">
-        <v>8981.8591567221847</v>
+        <v>10771.970105609627</v>
       </c>
       <c r="L3">
-        <v>11548.104630071381</v>
+        <v>13849.675850069521</v>
       </c>
       <c r="M3">
-        <v>14114.350103420577</v>
+        <v>16927.381594529412</v>
       </c>
       <c r="N3">
-        <v>2566.2454733491959</v>
+        <v>3077.7057444598936</v>
       </c>
       <c r="O3">
-        <v>5132.4909466983918</v>
+        <v>6155.4114889197872</v>
       </c>
       <c r="P3">
-        <v>7698.7364200475877</v>
+        <v>9233.11723337968</v>
       </c>
       <c r="Q3">
-        <v>10264.981893396784</v>
+        <v>12310.822977839574</v>
       </c>
       <c r="R3">
-        <v>12831.227366745978</v>
+        <v>15388.528722299467</v>
       </c>
       <c r="S3">
-        <v>15397.472840095175</v>
+        <v>18466.234466759361</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -602,58 +602,58 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>453.58188518564361</v>
+        <v>478.35092910684779</v>
       </c>
       <c r="C4">
-        <v>2842.7543194664568</v>
+        <v>2997.9904717374829</v>
       </c>
       <c r="D4">
-        <v>7960.595125301058</v>
+        <v>8395.304571902534</v>
       </c>
       <c r="E4">
-        <v>15611.280528344996</v>
+        <v>16463.775977793019</v>
       </c>
       <c r="F4">
-        <v>25795.9767299594</v>
+        <v>27204.634574293763</v>
       </c>
       <c r="G4">
-        <v>38524.821386074145</v>
+        <v>40628.57161097051</v>
       </c>
       <c r="H4">
-        <v>1522.781081322451</v>
+        <v>1826.2774189119186</v>
       </c>
       <c r="I4">
-        <v>4568.3432439673534</v>
+        <v>5478.8322567357554</v>
       </c>
       <c r="J4">
-        <v>7613.9054066122544</v>
+        <v>9131.3870945595918</v>
       </c>
       <c r="K4">
-        <v>10659.467569257158</v>
+        <v>12783.94193238343</v>
       </c>
       <c r="L4">
-        <v>13705.029731902057</v>
+        <v>16436.496770207268</v>
       </c>
       <c r="M4">
-        <v>16750.59189454696</v>
+        <v>20089.051608031103</v>
       </c>
       <c r="N4">
-        <v>3045.5621626449019</v>
+        <v>3652.5548378238373</v>
       </c>
       <c r="O4">
-        <v>6091.1243252898039</v>
+        <v>7305.1096756476745</v>
       </c>
       <c r="P4">
-        <v>9136.6864879347067</v>
+        <v>10957.664513471511</v>
       </c>
       <c r="Q4">
-        <v>12182.248650579608</v>
+        <v>14610.219351295349</v>
       </c>
       <c r="R4">
-        <v>15227.810813224509</v>
+        <v>18262.774189119184</v>
       </c>
       <c r="S4">
-        <v>18273.372975869413</v>
+        <v>21915.329026943022</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -661,58 +661,58 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>631.72710826380569</v>
+        <v>660.10517320676161</v>
       </c>
       <c r="C5">
-        <v>3959.2519551480273</v>
+        <v>4137.1070885417921</v>
       </c>
       <c r="D5">
-        <v>11087.135317379636</v>
+        <v>11585.184937147658</v>
       </c>
       <c r="E5">
-        <v>21742.643228421828</v>
+        <v>22719.353161391831</v>
       </c>
       <c r="F5">
-        <v>35927.399917631148</v>
+        <v>37541.308953284446</v>
       </c>
       <c r="G5">
-        <v>53655.524626261096</v>
+        <v>56065.805810136721</v>
       </c>
       <c r="H5">
-        <v>1748.2215068049909</v>
+        <v>2096.6519671325095</v>
       </c>
       <c r="I5">
-        <v>5244.6645204149727</v>
+        <v>6289.9559013975286</v>
       </c>
       <c r="J5">
-        <v>8741.1075340249554</v>
+        <v>10483.259835662548</v>
       </c>
       <c r="K5">
-        <v>12237.550547634937</v>
+        <v>14676.563769927567</v>
       </c>
       <c r="L5">
-        <v>15733.993561244917</v>
+        <v>18869.867704192584</v>
       </c>
       <c r="M5">
-        <v>19230.4365748549</v>
+        <v>23063.171638457603</v>
       </c>
       <c r="N5">
-        <v>3496.4430136099818</v>
+        <v>4193.3039342650191</v>
       </c>
       <c r="O5">
-        <v>6992.8860272199636</v>
+        <v>8386.6078685300381</v>
       </c>
       <c r="P5">
-        <v>10489.329040829945</v>
+        <v>12579.911802795057</v>
       </c>
       <c r="Q5">
-        <v>13985.772054439927</v>
+        <v>16773.215737060076</v>
       </c>
       <c r="R5">
-        <v>17482.215068049911</v>
+        <v>20966.519671325095</v>
       </c>
       <c r="S5">
-        <v>20978.658081659891</v>
+        <v>25159.823605590114</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -720,58 +720,58 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>777.02668173487075</v>
+        <v>811.42019083598234</v>
       </c>
       <c r="C6">
-        <v>4869.8945614603344</v>
+        <v>5085.4505608335839</v>
       </c>
       <c r="D6">
-        <v>13637.2174834888</v>
+        <v>14240.841238833982</v>
       </c>
       <c r="E6">
-        <v>26743.531659354841</v>
+        <v>27927.279812594876</v>
       </c>
       <c r="F6">
-        <v>44190.834897179695</v>
+        <v>46146.85251915946</v>
       </c>
       <c r="G6">
-        <v>65996.493915972736</v>
+        <v>68917.694780108519</v>
       </c>
       <c r="H6">
-        <v>1962.2882031866266</v>
+        <v>2353.3836468297673</v>
       </c>
       <c r="I6">
-        <v>5886.86460955988</v>
+        <v>7060.1509404893013</v>
       </c>
       <c r="J6">
-        <v>9811.4410159331328</v>
+        <v>11766.918234148836</v>
       </c>
       <c r="K6">
-        <v>13736.017422306386</v>
+        <v>16473.685527808371</v>
       </c>
       <c r="L6">
-        <v>17660.593828679641</v>
+        <v>21180.452821467905</v>
       </c>
       <c r="M6">
-        <v>21585.17023505289</v>
+        <v>25887.220115127438</v>
       </c>
       <c r="N6">
-        <v>3924.5764063732531</v>
+        <v>4706.7672936595345</v>
       </c>
       <c r="O6">
-        <v>7849.1528127465062</v>
+        <v>9413.534587319069</v>
       </c>
       <c r="P6">
-        <v>11773.729219119759</v>
+        <v>14120.301880978603</v>
       </c>
       <c r="Q6">
-        <v>15698.305625493013</v>
+        <v>18827.069174638138</v>
       </c>
       <c r="R6">
-        <v>19622.882031866266</v>
+        <v>23533.836468297672</v>
       </c>
       <c r="S6">
-        <v>23547.458438239519</v>
+        <v>28240.603761957205</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -779,58 +779,58 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>973.72599329729121</v>
+        <v>1014.7647303367646</v>
       </c>
       <c r="C7">
-        <v>6102.6770773478256</v>
+        <v>6359.88101514764</v>
       </c>
       <c r="D7">
-        <v>17089.391461144463</v>
+        <v>17809.642380978337</v>
       </c>
       <c r="E7">
-        <v>33513.4848537521</v>
+        <v>34925.946985457354</v>
       </c>
       <c r="F7">
-        <v>55377.460795580613</v>
+        <v>57711.403883417763</v>
       </c>
       <c r="G7">
-        <v>82703.082278963731</v>
+        <v>86188.693292085867</v>
       </c>
       <c r="H7">
-        <v>2173.101283754479</v>
+        <v>2606.2140490224133</v>
       </c>
       <c r="I7">
-        <v>6519.3038512634375</v>
+        <v>7818.64214706724</v>
       </c>
       <c r="J7">
-        <v>10865.506418772397</v>
+        <v>13031.070245112069</v>
       </c>
       <c r="K7">
-        <v>15211.708986281356</v>
+        <v>18243.498343156894</v>
       </c>
       <c r="L7">
-        <v>19557.911553790313</v>
+        <v>23455.926441201722</v>
       </c>
       <c r="M7">
-        <v>23904.11412129927</v>
+        <v>28668.354539246549</v>
       </c>
       <c r="N7">
-        <v>4346.2025675089581</v>
+        <v>5212.4280980448266</v>
       </c>
       <c r="O7">
-        <v>8692.4051350179161</v>
+        <v>10424.856196089653</v>
       </c>
       <c r="P7">
-        <v>13038.607702526875</v>
+        <v>15637.284294134481</v>
       </c>
       <c r="Q7">
-        <v>17384.810270035832</v>
+        <v>20849.712392179306</v>
       </c>
       <c r="R7">
-        <v>21731.012837544793</v>
+        <v>26062.140490224137</v>
       </c>
       <c r="S7">
-        <v>26077.21540505375</v>
+        <v>31274.568588268961</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -838,58 +838,58 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1170.5377967145905</v>
+        <v>1221.0483956735177</v>
       </c>
       <c r="C8">
-        <v>7336.16461853903</v>
+        <v>7652.7319861061</v>
       </c>
       <c r="D8">
-        <v>20543.539728649066</v>
+        <v>21430.026691601524</v>
       </c>
       <c r="E8">
-        <v>40287.309767812396</v>
+        <v>42025.772338203205</v>
       </c>
       <c r="F8">
-        <v>66570.484297954579</v>
+        <v>69443.108355300938</v>
       </c>
       <c r="G8">
-        <v>99419.225098951676</v>
+        <v>103709.32544588212</v>
       </c>
       <c r="H8">
-        <v>2377.1431985391564</v>
+        <v>2850.922242699784</v>
       </c>
       <c r="I8">
-        <v>7131.42959561747</v>
+        <v>8552.7667280993537</v>
       </c>
       <c r="J8">
-        <v>11885.715992695783</v>
+        <v>14254.611213498922</v>
       </c>
       <c r="K8">
-        <v>16640.002389774098</v>
+        <v>19956.455698898491</v>
       </c>
       <c r="L8">
-        <v>21394.288786852409</v>
+        <v>25658.300184298056</v>
       </c>
       <c r="M8">
-        <v>26148.575183930723</v>
+        <v>31360.144669697627</v>
       </c>
       <c r="N8">
-        <v>4754.2863970783128</v>
+        <v>5701.8444853995679</v>
       </c>
       <c r="O8">
-        <v>9508.5727941566256</v>
+        <v>11403.688970799136</v>
       </c>
       <c r="P8">
-        <v>14262.85919123494</v>
+        <v>17105.533456198707</v>
       </c>
       <c r="Q8">
-        <v>19017.145588313251</v>
+        <v>22807.377941598272</v>
       </c>
       <c r="R8">
-        <v>23771.431985391566</v>
+        <v>28509.222426997843</v>
       </c>
       <c r="S8">
-        <v>28525.71838246988</v>
+        <v>34211.066912397415</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -897,58 +897,58 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1249.466765224849</v>
+        <v>1317.9862404900896</v>
       </c>
       <c r="C9">
-        <v>7830.8397223997954</v>
+        <v>8260.2749371639729</v>
       </c>
       <c r="D9">
-        <v>21928.78367795415</v>
+        <v>23131.335672642857</v>
       </c>
       <c r="E9">
-        <v>43003.8694662277</v>
+        <v>45362.157539356682</v>
       </c>
       <c r="F9">
-        <v>71059.309582890739</v>
+        <v>74956.129202941826</v>
       </c>
       <c r="G9">
-        <v>106123.02988780533</v>
+        <v>111942.70794875904</v>
       </c>
       <c r="H9">
-        <v>2547.753757159433</v>
+        <v>3055.5311491984176</v>
       </c>
       <c r="I9">
-        <v>7643.261271478299</v>
+        <v>9166.5934475952527</v>
       </c>
       <c r="J9">
-        <v>12738.768785797165</v>
+        <v>15277.655745992086</v>
       </c>
       <c r="K9">
-        <v>17834.276300116031</v>
+        <v>21388.718044388923</v>
       </c>
       <c r="L9">
-        <v>22929.783814434897</v>
+        <v>27499.780342785754</v>
       </c>
       <c r="M9">
-        <v>28025.291328753759</v>
+        <v>33610.842641182593</v>
       </c>
       <c r="N9">
-        <v>5095.507514318866</v>
+        <v>6111.0622983968351</v>
       </c>
       <c r="O9">
-        <v>10191.015028637732</v>
+        <v>12222.12459679367</v>
       </c>
       <c r="P9">
-        <v>15286.522542956598</v>
+        <v>18333.186895190505</v>
       </c>
       <c r="Q9">
-        <v>20382.030057275464</v>
+        <v>24444.24919358734</v>
       </c>
       <c r="R9">
-        <v>25477.53757159433</v>
+        <v>30555.311491984172</v>
       </c>
       <c r="S9">
-        <v>30573.045085913196</v>
+        <v>36666.373790381011</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -956,58 +956,58 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1367.1960732050893</v>
+        <v>1457.3960877704367</v>
       </c>
       <c r="C10">
-        <v>8568.6899534592831</v>
+        <v>9134.0045954155667</v>
       </c>
       <c r="D10">
-        <v>23994.993519709602</v>
+        <v>25578.050118094485</v>
       </c>
       <c r="E10">
-        <v>47055.850626223168</v>
+        <v>50160.33468308561</v>
       </c>
       <c r="F10">
-        <v>77754.776461709174</v>
+        <v>82884.605391754245</v>
       </c>
       <c r="G10">
-        <v>116122.32816222509</v>
+        <v>123783.43537052785</v>
       </c>
       <c r="H10">
-        <v>2677.9949654333482</v>
+        <v>3211.726411157103</v>
       </c>
       <c r="I10">
-        <v>8033.9848963000441</v>
+        <v>9635.1792334713082</v>
       </c>
       <c r="J10">
-        <v>13389.974827166741</v>
+        <v>16058.632055785516</v>
       </c>
       <c r="K10">
-        <v>18745.964758033435</v>
+        <v>22482.084878099718</v>
       </c>
       <c r="L10">
-        <v>24101.954688900132</v>
+        <v>28905.537700413926</v>
       </c>
       <c r="M10">
-        <v>29457.944619766829</v>
+        <v>35328.990522728134</v>
       </c>
       <c r="N10">
-        <v>5355.9899308666963</v>
+        <v>6423.4528223142061</v>
       </c>
       <c r="O10">
-        <v>10711.979861733393</v>
+        <v>12846.905644628412</v>
       </c>
       <c r="P10">
-        <v>16067.969792600088</v>
+        <v>19270.358466942616</v>
       </c>
       <c r="Q10">
-        <v>21423.959723466785</v>
+        <v>25693.811289256824</v>
       </c>
       <c r="R10">
-        <v>26779.949654333483</v>
+        <v>32117.264111571032</v>
       </c>
       <c r="S10">
-        <v>32135.939585200176</v>
+        <v>38540.716933885233</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1015,58 +1015,58 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1237.1741020153365</v>
+        <v>1326.1911927847698</v>
       </c>
       <c r="C11">
-        <v>7753.7973567808813</v>
+        <v>8311.6982067841254</v>
       </c>
       <c r="D11">
-        <v>21713.041122930012</v>
+        <v>23275.33680093665</v>
       </c>
       <c r="E11">
-        <v>42580.783315585621</v>
+        <v>45644.553764112257</v>
       </c>
       <c r="F11">
-        <v>70360.204824833578</v>
+        <v>75422.758857645444</v>
       </c>
       <c r="G11">
-        <v>105078.95676678151</v>
+        <v>112639.59274940411</v>
       </c>
       <c r="H11">
-        <v>2165.1507536856857</v>
+        <v>2596.6698264062597</v>
       </c>
       <c r="I11">
-        <v>6495.4522610570575</v>
+        <v>7790.0094792187792</v>
       </c>
       <c r="J11">
-        <v>10825.753768428429</v>
+        <v>12983.349132031299</v>
       </c>
       <c r="K11">
-        <v>15156.0552757998</v>
+        <v>18176.688784843816</v>
       </c>
       <c r="L11">
-        <v>19486.35678317117</v>
+        <v>23370.028437656336</v>
       </c>
       <c r="M11">
-        <v>23816.658290542542</v>
+        <v>28563.368090468855</v>
       </c>
       <c r="N11">
-        <v>4330.3015073713714</v>
+        <v>5193.3396528125195</v>
       </c>
       <c r="O11">
-        <v>8660.6030147427427</v>
+        <v>10386.679305625039</v>
       </c>
       <c r="P11">
-        <v>12990.904522114115</v>
+        <v>15580.018958437559</v>
       </c>
       <c r="Q11">
-        <v>17321.206029485485</v>
+        <v>20773.358611250078</v>
       </c>
       <c r="R11">
-        <v>21651.507536856858</v>
+        <v>25966.698264062597</v>
       </c>
       <c r="S11">
-        <v>25981.80904422823</v>
+        <v>31160.037916875117</v>
       </c>
     </row>
   </sheetData>

--- a/src/nodes/HPC/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/HPC/compressor_blade_self_frequency.xlsx
@@ -1076,9 +1076,735 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ν0.изг.rotor6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor3</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor4</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor5</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor6</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage4</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage5</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ν0.угл.rotor_bondage6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Гц</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>290.31431070612922</v>
+      </c>
+      <c r="C3">
+        <v>1819.5000455650852</v>
+      </c>
+      <c r="D3">
+        <v>5095.16530993398</v>
+      </c>
+      <c r="E3">
+        <v>9991.9734315922869</v>
+      </c>
+      <c r="F3">
+        <v>16510.670835728837</v>
+      </c>
+      <c r="G3">
+        <v>24657.746111702203</v>
+      </c>
+      <c r="H3">
+        <v>852.26518743295708</v>
+      </c>
+      <c r="I3">
+        <v>2556.7955622988716</v>
+      </c>
+      <c r="J3">
+        <v>4261.3259371647855</v>
+      </c>
+      <c r="K3">
+        <v>5965.8563120307</v>
+      </c>
+      <c r="L3">
+        <v>7670.3866868966134</v>
+      </c>
+      <c r="M3">
+        <v>9374.9170617625277</v>
+      </c>
+      <c r="N3">
+        <v>1704.5303748659142</v>
+      </c>
+      <c r="O3">
+        <v>3409.0607497318283</v>
+      </c>
+      <c r="P3">
+        <v>5113.5911245977431</v>
+      </c>
+      <c r="Q3">
+        <v>6818.1214994636566</v>
+      </c>
+      <c r="R3">
+        <v>8522.651874329571</v>
+      </c>
+      <c r="S3">
+        <v>10227.182249195486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>376.82866942135126</v>
+      </c>
+      <c r="C4">
+        <v>2361.7154094632915</v>
+      </c>
+      <c r="D4">
+        <v>6613.5367545410936</v>
+      </c>
+      <c r="E4">
+        <v>12969.605404439752</v>
+      </c>
+      <c r="F4">
+        <v>21430.890220839028</v>
+      </c>
+      <c r="G4">
+        <v>32005.813408240196</v>
+      </c>
+      <c r="H4">
+        <v>1017.6786409479544</v>
+      </c>
+      <c r="I4">
+        <v>3053.0359228438629</v>
+      </c>
+      <c r="J4">
+        <v>5088.3932047397711</v>
+      </c>
+      <c r="K4">
+        <v>7123.75048663568</v>
+      </c>
+      <c r="L4">
+        <v>9159.10776853159</v>
+      </c>
+      <c r="M4">
+        <v>11194.465050427498</v>
+      </c>
+      <c r="N4">
+        <v>2035.3572818959087</v>
+      </c>
+      <c r="O4">
+        <v>4070.7145637918175</v>
+      </c>
+      <c r="P4">
+        <v>6106.0718456877257</v>
+      </c>
+      <c r="Q4">
+        <v>8141.4291275836349</v>
+      </c>
+      <c r="R4">
+        <v>10176.786409479542</v>
+      </c>
+      <c r="S4">
+        <v>12212.143691375452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>468.7237502830244</v>
+      </c>
+      <c r="C5">
+        <v>2937.6536172916781</v>
+      </c>
+      <c r="D5">
+        <v>8226.3426373138918</v>
+      </c>
+      <c r="E5">
+        <v>16132.429876407738</v>
+      </c>
+      <c r="F5">
+        <v>26657.12046708275</v>
+      </c>
+      <c r="G5">
+        <v>39810.890489318583</v>
+      </c>
+      <c r="H5">
+        <v>1194.0528032656057</v>
+      </c>
+      <c r="I5">
+        <v>3582.1584097968171</v>
+      </c>
+      <c r="J5">
+        <v>5970.2640163280284</v>
+      </c>
+      <c r="K5">
+        <v>8358.36962285924</v>
+      </c>
+      <c r="L5">
+        <v>10746.475229390451</v>
+      </c>
+      <c r="M5">
+        <v>13134.580835921661</v>
+      </c>
+      <c r="N5">
+        <v>2388.1056065312114</v>
+      </c>
+      <c r="O5">
+        <v>4776.2112130624228</v>
+      </c>
+      <c r="P5">
+        <v>7164.3168195936341</v>
+      </c>
+      <c r="Q5">
+        <v>9552.4224261248455</v>
+      </c>
+      <c r="R5">
+        <v>11940.528032656057</v>
+      </c>
+      <c r="S5">
+        <v>14328.633639187268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>542.88192416326592</v>
+      </c>
+      <c r="C6">
+        <v>3402.4285036068986</v>
+      </c>
+      <c r="D6">
+        <v>9527.85668973391</v>
+      </c>
+      <c r="E6">
+        <v>18684.789425423693</v>
+      </c>
+      <c r="F6">
+        <v>30874.622510772257</v>
+      </c>
+      <c r="G6">
+        <v>46109.489477425079</v>
+      </c>
+      <c r="H6">
+        <v>1351.5668631617573</v>
+      </c>
+      <c r="I6">
+        <v>4054.7005894852723</v>
+      </c>
+      <c r="J6">
+        <v>6757.8343158087873</v>
+      </c>
+      <c r="K6">
+        <v>9460.968042132301</v>
+      </c>
+      <c r="L6">
+        <v>12164.101768455816</v>
+      </c>
+      <c r="M6">
+        <v>14867.235494779332</v>
+      </c>
+      <c r="N6">
+        <v>2703.1337263235146</v>
+      </c>
+      <c r="O6">
+        <v>5406.2674526470291</v>
+      </c>
+      <c r="P6">
+        <v>8109.4011789705446</v>
+      </c>
+      <c r="Q6">
+        <v>10812.534905294058</v>
+      </c>
+      <c r="R6">
+        <v>13515.668631617575</v>
+      </c>
+      <c r="S6">
+        <v>16218.802357941089</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>624.88399618250924</v>
+      </c>
+      <c r="C7">
+        <v>3916.3638084581821</v>
+      </c>
+      <c r="D7">
+        <v>10967.035184513967</v>
+      </c>
+      <c r="E7">
+        <v>21507.118517499337</v>
+      </c>
+      <c r="F7">
+        <v>35538.220442491</v>
+      </c>
+      <c r="G7">
+        <v>53074.307255666739</v>
+      </c>
+      <c r="H7">
+        <v>1506.3378841291112</v>
+      </c>
+      <c r="I7">
+        <v>4519.0136523873343</v>
+      </c>
+      <c r="J7">
+        <v>7531.6894206455572</v>
+      </c>
+      <c r="K7">
+        <v>10544.365188903779</v>
+      </c>
+      <c r="L7">
+        <v>13557.040957162004</v>
+      </c>
+      <c r="M7">
+        <v>16569.716725420225</v>
+      </c>
+      <c r="N7">
+        <v>3012.6757682582224</v>
+      </c>
+      <c r="O7">
+        <v>6025.3515365164449</v>
+      </c>
+      <c r="P7">
+        <v>9038.0273047746687</v>
+      </c>
+      <c r="Q7">
+        <v>12050.70307303289</v>
+      </c>
+      <c r="R7">
+        <v>15063.378841291114</v>
+      </c>
+      <c r="S7">
+        <v>18076.054609549337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>703.18889436527786</v>
+      </c>
+      <c r="C8">
+        <v>4407.127648053186</v>
+      </c>
+      <c r="D8">
+        <v>12341.326378938133</v>
+      </c>
+      <c r="E8">
+        <v>24202.199102065384</v>
+      </c>
+      <c r="F8">
+        <v>39991.55378171333</v>
+      </c>
+      <c r="G8">
+        <v>59725.106845935217</v>
+      </c>
+      <c r="H8">
+        <v>1659.6073807954558</v>
+      </c>
+      <c r="I8">
+        <v>4978.8221423863679</v>
+      </c>
+      <c r="J8">
+        <v>8298.03690397728</v>
+      </c>
+      <c r="K8">
+        <v>11617.251665568192</v>
+      </c>
+      <c r="L8">
+        <v>14936.466427159103</v>
+      </c>
+      <c r="M8">
+        <v>18255.681188750015</v>
+      </c>
+      <c r="N8">
+        <v>3319.2147615909116</v>
+      </c>
+      <c r="O8">
+        <v>6638.4295231818232</v>
+      </c>
+      <c r="P8">
+        <v>9957.6442847727358</v>
+      </c>
+      <c r="Q8">
+        <v>13276.859046363647</v>
+      </c>
+      <c r="R8">
+        <v>16596.073807954559</v>
+      </c>
+      <c r="S8">
+        <v>19915.288569545472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>758.74950061951813</v>
+      </c>
+      <c r="C9">
+        <v>4755.3451553656141</v>
+      </c>
+      <c r="D9">
+        <v>13316.443564504865</v>
+      </c>
+      <c r="E9">
+        <v>26114.471701322436</v>
+      </c>
+      <c r="F9">
+        <v>43151.380381601055</v>
+      </c>
+      <c r="G9">
+        <v>64444.127825290569</v>
+      </c>
+      <c r="H9">
+        <v>1796.4928565377422</v>
+      </c>
+      <c r="I9">
+        <v>5389.4785696132258</v>
+      </c>
+      <c r="J9">
+        <v>8982.46428268871</v>
+      </c>
+      <c r="K9">
+        <v>12575.449995764193</v>
+      </c>
+      <c r="L9">
+        <v>16168.435708839679</v>
+      </c>
+      <c r="M9">
+        <v>19761.421421915162</v>
+      </c>
+      <c r="N9">
+        <v>3592.9857130754845</v>
+      </c>
+      <c r="O9">
+        <v>7185.9714261509689</v>
+      </c>
+      <c r="P9">
+        <v>10778.957139226452</v>
+      </c>
+      <c r="Q9">
+        <v>14371.942852301938</v>
+      </c>
+      <c r="R9">
+        <v>17964.92856537742</v>
+      </c>
+      <c r="S9">
+        <v>21557.914278452903</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>814.23021348102861</v>
+      </c>
+      <c r="C10">
+        <v>5103.0619431945315</v>
+      </c>
+      <c r="D10">
+        <v>14290.158579981737</v>
+      </c>
+      <c r="E10">
+        <v>28023.994547542603</v>
+      </c>
+      <c r="F10">
+        <v>46306.663307750823</v>
+      </c>
+      <c r="G10">
+        <v>69156.363086817728</v>
+      </c>
+      <c r="H10">
+        <v>1903.1859535804524</v>
+      </c>
+      <c r="I10">
+        <v>5709.5578607413572</v>
+      </c>
+      <c r="J10">
+        <v>9515.929767902262</v>
+      </c>
+      <c r="K10">
+        <v>13322.301675063167</v>
+      </c>
+      <c r="L10">
+        <v>17128.67358222407</v>
+      </c>
+      <c r="M10">
+        <v>20935.045489384975</v>
+      </c>
+      <c r="N10">
+        <v>3806.3719071609048</v>
+      </c>
+      <c r="O10">
+        <v>7612.74381432181</v>
+      </c>
+      <c r="P10">
+        <v>11419.115721482714</v>
+      </c>
+      <c r="Q10">
+        <v>15225.487628643619</v>
+      </c>
+      <c r="R10">
+        <v>19031.859535804524</v>
+      </c>
+      <c r="S10">
+        <v>22838.231442965429</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>669.42052086831166</v>
+      </c>
+      <c r="C11">
+        <v>4195.4895894023912</v>
+      </c>
+      <c r="D11">
+        <v>11748.674074626482</v>
+      </c>
+      <c r="E11">
+        <v>23039.966727129802</v>
+      </c>
+      <c r="F11">
+        <v>38071.088689550765</v>
+      </c>
+      <c r="G11">
+        <v>56857.00165929088</v>
+      </c>
+      <c r="H11">
+        <v>1513.4646084021522</v>
+      </c>
+      <c r="I11">
+        <v>4540.3938252064554</v>
+      </c>
+      <c r="J11">
+        <v>7567.32304201076</v>
+      </c>
+      <c r="K11">
+        <v>10594.252258815064</v>
+      </c>
+      <c r="L11">
+        <v>13621.181475619369</v>
+      </c>
+      <c r="M11">
+        <v>16648.110692423674</v>
+      </c>
+      <c r="N11">
+        <v>3026.9292168043044</v>
+      </c>
+      <c r="O11">
+        <v>6053.8584336086087</v>
+      </c>
+      <c r="P11">
+        <v>9080.78765041291</v>
+      </c>
+      <c r="Q11">
+        <v>12107.716867217217</v>
+      </c>
+      <c r="R11">
+        <v>15134.64608402152</v>
+      </c>
+      <c r="S11">
+        <v>18161.575300825822</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/nodes/HPC/compressor_blade_self_frequency.xlsx
+++ b/src/nodes/HPC/compressor_blade_self_frequency.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\projects\gte\src\nodes\HPC\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="210" windowWidth="15135" windowHeight="6720"/>
+    <workbookView xWindow="600" yWindow="216" windowWidth="15132" windowHeight="6720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,9 +20,131 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>ν0.изг.stator1</t>
+  </si>
+  <si>
+    <t>ν0.изг.stator2</t>
+  </si>
+  <si>
+    <t>ν0.изг.stator3</t>
+  </si>
+  <si>
+    <t>ν0.изг.stator4</t>
+  </si>
+  <si>
+    <t>ν0.изг.stator5</t>
+  </si>
+  <si>
+    <t>ν0.изг.stator6</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator1</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator2</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator3</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator4</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator5</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator6</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator_bondage1</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator_bondage2</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator_bondage3</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator_bondage4</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator_bondage5</t>
+  </si>
+  <si>
+    <t>ν0.угл.stator_bondage6</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Гц</t>
+  </si>
+  <si>
+    <t>ν0.изг.rotor1</t>
+  </si>
+  <si>
+    <t>ν0.изг.rotor2</t>
+  </si>
+  <si>
+    <t>ν0.изг.rotor3</t>
+  </si>
+  <si>
+    <t>ν0.изг.rotor4</t>
+  </si>
+  <si>
+    <t>ν0.изг.rotor5</t>
+  </si>
+  <si>
+    <t>ν0.изг.rotor6</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor1</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor2</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor3</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor4</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor5</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor6</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor_bondage1</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor_bondage2</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor_bondage3</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor_bondage4</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor_bondage5</t>
+  </si>
+  <si>
+    <t>ν0.угл.rotor_bondage6</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -45,21 +172,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -97,9 +233,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -131,9 +267,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -165,9 +302,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -340,1467 +478,1324 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="20" width="13.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ν0.изг.stator1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ν0.изг.stator2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ν0.изг.stator3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ν0.изг.stator4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ν0.изг.stator5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ν0.изг.stator6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator1</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator2</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator3</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator4</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator5</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator6</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator_bondage1</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator_bondage2</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator_bondage3</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator_bondage4</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator_bondage5</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ν0.угл.stator_bondage6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
         <v>320.81601986011196</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>2010.6647906322426</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>5630.4859766867248</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>11041.774479096477</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>18245.355145791389</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>27248.398286107782</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>1538.8528722299468</v>
       </c>
-      <c r="I3">
-        <v>4616.55861668984</v>
-      </c>
-      <c r="J3">
+      <c r="I3" s="1">
+        <v>4616.5586166898402</v>
+      </c>
+      <c r="J3" s="1">
         <v>7694.2643611497333</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>10771.970105609627</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>13849.675850069521</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>16927.381594529412</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>3077.7057444598936</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>6155.4114889197872</v>
       </c>
-      <c r="P3">
-        <v>9233.11723337968</v>
-      </c>
-      <c r="Q3">
+      <c r="P3" s="1">
+        <v>9233.1172333796803</v>
+      </c>
+      <c r="Q3" s="1">
         <v>12310.822977839574</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>15388.528722299467</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>18466.234466759361</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
-      <c r="A4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>478.35092910684779</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>2997.9904717374829</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>8395.304571902534</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>16463.775977793019</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>27204.634574293763</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>40628.57161097051</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1826.2774189119186</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>5478.8322567357554</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>9131.3870945595918</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>12783.94193238343</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>16436.496770207268</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>20089.051608031103</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>3652.5548378238373</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>7305.1096756476745</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>10957.664513471511</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>14610.219351295349</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>18262.774189119184</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>21915.329026943022</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
-      <c r="A5">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>660.10517320676161</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>4137.1070885417921</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>11585.184937147658</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>22719.353161391831</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>37541.308953284446</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>56065.805810136721</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>2096.6519671325095</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>6289.9559013975286</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>10483.259835662548</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>14676.563769927567</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>18869.867704192584</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>23063.171638457603</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>4193.3039342650191</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>8386.6078685300381</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>12579.911802795057</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>16773.215737060076</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>20966.519671325095</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>25159.823605590114</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
-      <c r="A6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>811.42019083598234</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>5085.4505608335839</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>14240.841238833982</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>27927.279812594876</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>46146.85251915946</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>68917.694780108519</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2353.3836468297673</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>7060.1509404893013</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>11766.918234148836</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>16473.685527808371</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>21180.452821467905</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>25887.220115127438</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>4706.7672936595345</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>9413.534587319069</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>14120.301880978603</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>18827.069174638138</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>23533.836468297672</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>28240.603761957205</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
-      <c r="A7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>1014.7647303367646</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>6359.88101514764</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>17809.642380978337</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>34925.946985457354</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>57711.403883417763</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>86188.693292085867</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>2606.2140490224133</v>
       </c>
-      <c r="I7">
-        <v>7818.64214706724</v>
-      </c>
-      <c r="J7">
+      <c r="I7" s="1">
+        <v>7818.6421470672403</v>
+      </c>
+      <c r="J7" s="1">
         <v>13031.070245112069</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>18243.498343156894</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>23455.926441201722</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>28668.354539246549</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>5212.4280980448266</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>10424.856196089653</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>15637.284294134481</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>20849.712392179306</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>26062.140490224137</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>31274.568588268961</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
-      <c r="A8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>1221.0483956735177</v>
       </c>
-      <c r="C8">
-        <v>7652.7319861061</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="1">
+        <v>7652.7319861060996</v>
+      </c>
+      <c r="D8" s="1">
         <v>21430.026691601524</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>42025.772338203205</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>69443.108355300938</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>103709.32544588212</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>2850.922242699784</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>8552.7667280993537</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>14254.611213498922</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>19956.455698898491</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>25658.300184298056</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>31360.144669697627</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>5701.8444853995679</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>11403.688970799136</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>17105.533456198707</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>22807.377941598272</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>28509.222426997843</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>34211.066912397415</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
-      <c r="A9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>1317.9862404900896</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>8260.2749371639729</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>23131.335672642857</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>45362.157539356682</v>
       </c>
-      <c r="F9">
-        <v>74956.129202941826</v>
-      </c>
-      <c r="G9">
+      <c r="F9" s="1">
+        <v>74956.129202941825</v>
+      </c>
+      <c r="G9" s="1">
         <v>111942.70794875904</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>3055.5311491984176</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>9166.5934475952527</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>15277.655745992086</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>21388.718044388923</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>27499.780342785754</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>33610.842641182593</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>6111.0622983968351</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>12222.12459679367</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>18333.186895190505</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>24444.24919358734</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>30555.311491984172</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>36666.373790381011</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
-      <c r="A10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>1457.3960877704367</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>9134.0045954155667</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>25578.050118094485</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>50160.33468308561</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>82884.605391754245</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>123783.43537052785</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>3211.726411157103</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>9635.1792334713082</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>16058.632055785516</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>22482.084878099718</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>28905.537700413926</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>35328.990522728134</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>6423.4528223142061</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>12846.905644628412</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>19270.358466942616</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>25693.811289256824</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>32117.264111571032</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>38540.716933885233</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
-      <c r="A11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>1326.1911927847698</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>8311.6982067841254</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>23275.33680093665</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>45644.553764112257</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>75422.758857645444</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>112639.59274940411</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>2596.6698264062597</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>7790.0094792187792</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>12983.349132031299</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>18176.688784843816</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>23370.028437656336</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>28563.368090468855</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>5193.3396528125195</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>10386.679305625039</v>
       </c>
-      <c r="P11">
-        <v>15580.018958437559</v>
-      </c>
-      <c r="Q11">
+      <c r="P11" s="1">
+        <v>15580.018958437558</v>
+      </c>
+      <c r="Q11" s="1">
         <v>20773.358611250078</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>25966.698264062597</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>31160.037916875117</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="19" width="13.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ν0.изг.rotor1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ν0.изг.rotor2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ν0.изг.rotor3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ν0.изг.rotor4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ν0.изг.rotor5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ν0.изг.rotor6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor1</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor2</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor3</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor4</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor5</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor6</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor_bondage1</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor_bondage2</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor_bondage3</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor_bondage4</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor_bondage5</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>ν0.угл.rotor_bondage6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Гц</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>290.31431070612922</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1819.5000455650852</v>
       </c>
-      <c r="D3">
-        <v>5095.16530993398</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="1">
+        <v>5095.1653099339801</v>
+      </c>
+      <c r="E3" s="1">
         <v>9991.9734315922869</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>16510.670835728837</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>24657.746111702203</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>852.26518743295708</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>2556.7955622988716</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>4261.3259371647855</v>
       </c>
-      <c r="K3">
-        <v>5965.8563120307</v>
-      </c>
-      <c r="L3">
+      <c r="K3" s="1">
+        <v>5965.8563120306999</v>
+      </c>
+      <c r="L3" s="1">
         <v>7670.3866868966134</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>9374.9170617625277</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>1704.5303748659142</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>3409.0607497318283</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>5113.5911245977431</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>6818.1214994636566</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>8522.651874329571</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>10227.182249195486</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
-      <c r="A4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>376.82866942135126</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>2361.7154094632915</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>6613.5367545410936</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>12969.605404439752</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>21430.890220839028</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>32005.813408240196</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1017.6786409479544</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>3053.0359228438629</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>5088.3932047397711</v>
       </c>
-      <c r="K4">
-        <v>7123.75048663568</v>
-      </c>
-      <c r="L4">
-        <v>9159.10776853159</v>
-      </c>
-      <c r="M4">
+      <c r="K4" s="1">
+        <v>7123.7504866356803</v>
+      </c>
+      <c r="L4" s="1">
+        <v>9159.1077685315904</v>
+      </c>
+      <c r="M4" s="1">
         <v>11194.465050427498</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>2035.3572818959087</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>4070.7145637918175</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>6106.0718456877257</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>8141.4291275836349</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>10176.786409479542</v>
       </c>
-      <c r="S4">
-        <v>12212.143691375452</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5">
+      <c r="S4" s="1">
+        <v>12212.143691375451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>468.7237502830244</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>2937.6536172916781</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>8226.3426373138918</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>16132.429876407738</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>26657.12046708275</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>39810.890489318583</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1194.0528032656057</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>3582.1584097968171</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>5970.2640163280284</v>
       </c>
-      <c r="K5">
-        <v>8358.36962285924</v>
-      </c>
-      <c r="L5">
+      <c r="K5" s="1">
+        <v>8358.3696228592398</v>
+      </c>
+      <c r="L5" s="1">
         <v>10746.475229390451</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>13134.580835921661</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>2388.1056065312114</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>4776.2112130624228</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>7164.3168195936341</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>9552.4224261248455</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>11940.528032656057</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>14328.633639187268</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
-      <c r="A6">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>542.88192416326592</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>3402.4285036068986</v>
       </c>
-      <c r="D6">
-        <v>9527.85668973391</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="1">
+        <v>9527.8566897339097</v>
+      </c>
+      <c r="E6" s="1">
         <v>18684.789425423693</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>30874.622510772257</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>46109.489477425079</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1351.5668631617573</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>4054.7005894852723</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>6757.8343158087873</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>9460.968042132301</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>12164.101768455816</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>14867.235494779332</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>2703.1337263235146</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>5406.2674526470291</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>8109.4011789705446</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>10812.534905294058</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>13515.668631617575</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>16218.802357941089</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
-      <c r="A7">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>624.88399618250924</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>3916.3638084581821</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>10967.035184513967</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>21507.118517499337</v>
       </c>
-      <c r="F7">
-        <v>35538.220442491</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="1">
+        <v>35538.220442491001</v>
+      </c>
+      <c r="G7" s="1">
         <v>53074.307255666739</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>1506.3378841291112</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>4519.0136523873343</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>7531.6894206455572</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>10544.365188903779</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>13557.040957162004</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>16569.716725420225</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>3012.6757682582224</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>6025.3515365164449</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>9038.0273047746687</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>12050.70307303289</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>15063.378841291114</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>18076.054609549337</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
-      <c r="A8">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>703.18889436527786</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>4407.127648053186</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>12341.326378938133</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>24202.199102065384</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>39991.55378171333</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>59725.106845935217</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>1659.6073807954558</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>4978.8221423863679</v>
       </c>
-      <c r="J8">
-        <v>8298.03690397728</v>
-      </c>
-      <c r="K8">
+      <c r="J8" s="1">
+        <v>8298.0369039772795</v>
+      </c>
+      <c r="K8" s="1">
         <v>11617.251665568192</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>14936.466427159103</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>18255.681188750015</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>3319.2147615909116</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>6638.4295231818232</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>9957.6442847727358</v>
       </c>
-      <c r="Q8">
-        <v>13276.859046363647</v>
-      </c>
-      <c r="R8">
+      <c r="Q8" s="1">
+        <v>13276.859046363646</v>
+      </c>
+      <c r="R8" s="1">
         <v>16596.073807954559</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>19915.288569545472</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
-      <c r="A9">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>758.74950061951813</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>4755.3451553656141</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>13316.443564504865</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>26114.471701322436</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>43151.380381601055</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>64444.127825290569</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>1796.4928565377422</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>5389.4785696132258</v>
       </c>
-      <c r="J9">
-        <v>8982.46428268871</v>
-      </c>
-      <c r="K9">
+      <c r="J9" s="1">
+        <v>8982.4642826887102</v>
+      </c>
+      <c r="K9" s="1">
         <v>12575.449995764193</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>16168.435708839679</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>19761.421421915162</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>3592.9857130754845</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>7185.9714261509689</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>10778.957139226452</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>14371.942852301938</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>17964.92856537742</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>21557.914278452903</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
-      <c r="A10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>814.23021348102861</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>5103.0619431945315</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>14290.158579981737</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>28023.994547542603</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>46306.663307750823</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>69156.363086817728</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>1903.1859535804524</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>5709.5578607413572</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>9515.929767902262</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>13322.301675063167</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>17128.67358222407</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>20935.045489384975</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>3806.3719071609048</v>
       </c>
-      <c r="O10">
-        <v>7612.74381432181</v>
-      </c>
-      <c r="P10">
+      <c r="O10" s="1">
+        <v>7612.7438143218096</v>
+      </c>
+      <c r="P10" s="1">
         <v>11419.115721482714</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>15225.487628643619</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>19031.859535804524</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>22838.231442965429</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
-      <c r="A11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>669.42052086831166</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>4195.4895894023912</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>11748.674074626482</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>23039.966727129802</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>38071.088689550765</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>56857.00165929088</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>1513.4646084021522</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>4540.3938252064554</v>
       </c>
-      <c r="J11">
-        <v>7567.32304201076</v>
-      </c>
-      <c r="K11">
+      <c r="J11" s="1">
+        <v>7567.3230420107602</v>
+      </c>
+      <c r="K11" s="1">
         <v>10594.252258815064</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>13621.181475619369</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>16648.110692423674</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>3026.9292168043044</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>6053.8584336086087</v>
       </c>
-      <c r="P11">
-        <v>9080.78765041291</v>
-      </c>
-      <c r="Q11">
+      <c r="P11" s="1">
+        <v>9080.7876504129108</v>
+      </c>
+      <c r="Q11" s="1">
         <v>12107.716867217217</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>15134.64608402152</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>18161.575300825822</v>
       </c>
     </row>
@@ -1810,9 +1805,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
